--- a/practice/module-1-workbook-security.xlsx
+++ b/practice/module-1-workbook-security.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Confidential Pricing" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Customer Quote" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Tasks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Solutions" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +53,24 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +80,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F6F3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -106,6 +128,16 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -768,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -933,6 +965,199 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Self-check:</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Right-click any sheet tab → Unhide → Solutions to reveal the answer key. Try every task FIRST without peeking.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Solutions — Module 1 — Workbook Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>These are the expected formulas / results for each Tasks sheet item. Try the task FIRST in real Excel, then peek here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Expected solution / formula</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Where it lands</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Document Inspector lists 'Hidden Worksheets', custom properties, and Internal Notes column on Confidential Pricing.</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>File → Info → Inspect Document</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Inspector report should flag at least the Internal Notes column on Confidential Pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Set password = mo211 via File → Info → Protect Workbook → Encrypt with Password.</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Whole workbook</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Closing &amp; reopening prompts for password 'mo211'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Step 1 (per cell): Format Cells → Protection → uncheck Locked on B3:B7. Step 2: Review → Protect Sheet (no password).</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Customer Quote!B3:B7</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Tab key cycles only B3:B7 once protected; other cells refuse edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Right-click 'Confidential Pricing' tab → Hide. Then Review → Protect Workbook → Structure.</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Workbook structure</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Unhide menu is greyed out after structure protection is on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Formulas → Calculation Options → Manual. Confirm B9 stays stale until F9.</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Whole workbook setting</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Customer Quote!B9 only refreshes when you press F9 (or Shift+F9 for sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Review → Check Accessibility. Pane lists missing alt text, default sheet names, etc.</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Whole workbook</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Accessibility pane should be empty (or only flag intentional warnings) after fixes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
